--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48109,14 +48109,14 @@
     <row r="750" ht="15" customHeight="1">
       <c r="A750" t="inlineStr">
         <is>
-          <t>A 3270-2024</t>
+          <t>A 3230-2024</t>
         </is>
       </c>
       <c r="B750" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         </is>
       </c>
       <c r="G750" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48223,14 +48223,14 @@
     <row r="752" ht="15" customHeight="1">
       <c r="A752" t="inlineStr">
         <is>
-          <t>A 3230-2024</t>
+          <t>A 3270-2024</t>
         </is>
       </c>
       <c r="B752" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         </is>
       </c>
       <c r="G752" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5920-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48651,8 +48651,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G759" t="n">
-        <v>9.9</v>
+        <v>17.8</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48694,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48709,7 +48714,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48746,14 +48751,14 @@
     <row r="761" ht="15" customHeight="1">
       <c r="A761" t="inlineStr">
         <is>
-          <t>A 5920-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B761" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48765,13 +48770,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G761" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z764"/>
+  <dimension ref="A1:Z769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48109,14 +48109,14 @@
     <row r="750" ht="15" customHeight="1">
       <c r="A750" t="inlineStr">
         <is>
-          <t>A 3230-2024</t>
+          <t>A 3186-2024</t>
         </is>
       </c>
       <c r="B750" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         </is>
       </c>
       <c r="G750" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -48166,14 +48166,14 @@
     <row r="751" ht="15" customHeight="1">
       <c r="A751" t="inlineStr">
         <is>
-          <t>A 3186-2024</t>
+          <t>A 3230-2024</t>
         </is>
       </c>
       <c r="B751" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         </is>
       </c>
       <c r="G751" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5920-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48651,13 +48651,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G759" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48701,7 +48696,7 @@
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48751,14 +48746,14 @@
     <row r="761" ht="15" customHeight="1">
       <c r="A761" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5920-2024</t>
         </is>
       </c>
       <c r="B761" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48770,8 +48765,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G761" t="n">
-        <v>8.800000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
       </c>
       <c r="R763" s="2" t="inlineStr"/>
     </row>
-    <row r="764">
+    <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
           <t>A 6053-2024</t>
@@ -48929,7 +48929,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48975,6 +48975,296 @@
         <v>0</v>
       </c>
       <c r="R764" s="2" t="inlineStr"/>
+    </row>
+    <row r="765" ht="15" customHeight="1">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>A 6351-2024</t>
+        </is>
+      </c>
+      <c r="B765" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C765" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G765" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H765" t="n">
+        <v>0</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0</v>
+      </c>
+      <c r="J765" t="n">
+        <v>0</v>
+      </c>
+      <c r="K765" t="n">
+        <v>0</v>
+      </c>
+      <c r="L765" t="n">
+        <v>0</v>
+      </c>
+      <c r="M765" t="n">
+        <v>0</v>
+      </c>
+      <c r="N765" t="n">
+        <v>0</v>
+      </c>
+      <c r="O765" t="n">
+        <v>0</v>
+      </c>
+      <c r="P765" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q765" t="n">
+        <v>0</v>
+      </c>
+      <c r="R765" s="2" t="inlineStr"/>
+    </row>
+    <row r="766" ht="15" customHeight="1">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>A 6402-2024</t>
+        </is>
+      </c>
+      <c r="B766" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C766" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G766" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H766" t="n">
+        <v>0</v>
+      </c>
+      <c r="I766" t="n">
+        <v>0</v>
+      </c>
+      <c r="J766" t="n">
+        <v>0</v>
+      </c>
+      <c r="K766" t="n">
+        <v>0</v>
+      </c>
+      <c r="L766" t="n">
+        <v>0</v>
+      </c>
+      <c r="M766" t="n">
+        <v>0</v>
+      </c>
+      <c r="N766" t="n">
+        <v>0</v>
+      </c>
+      <c r="O766" t="n">
+        <v>0</v>
+      </c>
+      <c r="P766" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q766" t="n">
+        <v>0</v>
+      </c>
+      <c r="R766" s="2" t="inlineStr"/>
+    </row>
+    <row r="767" ht="15" customHeight="1">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>A 6376-2024</t>
+        </is>
+      </c>
+      <c r="B767" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C767" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G767" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H767" t="n">
+        <v>0</v>
+      </c>
+      <c r="I767" t="n">
+        <v>0</v>
+      </c>
+      <c r="J767" t="n">
+        <v>0</v>
+      </c>
+      <c r="K767" t="n">
+        <v>0</v>
+      </c>
+      <c r="L767" t="n">
+        <v>0</v>
+      </c>
+      <c r="M767" t="n">
+        <v>0</v>
+      </c>
+      <c r="N767" t="n">
+        <v>0</v>
+      </c>
+      <c r="O767" t="n">
+        <v>0</v>
+      </c>
+      <c r="P767" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q767" t="n">
+        <v>0</v>
+      </c>
+      <c r="R767" s="2" t="inlineStr"/>
+    </row>
+    <row r="768" ht="15" customHeight="1">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>A 6353-2024</t>
+        </is>
+      </c>
+      <c r="B768" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C768" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G768" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H768" t="n">
+        <v>0</v>
+      </c>
+      <c r="I768" t="n">
+        <v>0</v>
+      </c>
+      <c r="J768" t="n">
+        <v>0</v>
+      </c>
+      <c r="K768" t="n">
+        <v>0</v>
+      </c>
+      <c r="L768" t="n">
+        <v>0</v>
+      </c>
+      <c r="M768" t="n">
+        <v>0</v>
+      </c>
+      <c r="N768" t="n">
+        <v>0</v>
+      </c>
+      <c r="O768" t="n">
+        <v>0</v>
+      </c>
+      <c r="P768" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q768" t="n">
+        <v>0</v>
+      </c>
+      <c r="R768" s="2" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>A 6481-2024</t>
+        </is>
+      </c>
+      <c r="B769" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C769" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G769" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H769" t="n">
+        <v>0</v>
+      </c>
+      <c r="I769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" t="n">
+        <v>0</v>
+      </c>
+      <c r="K769" t="n">
+        <v>0</v>
+      </c>
+      <c r="L769" t="n">
+        <v>0</v>
+      </c>
+      <c r="M769" t="n">
+        <v>0</v>
+      </c>
+      <c r="N769" t="n">
+        <v>0</v>
+      </c>
+      <c r="O769" t="n">
+        <v>0</v>
+      </c>
+      <c r="P769" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q769" t="n">
+        <v>0</v>
+      </c>
+      <c r="R769" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48979,14 +48979,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49036,14 +49036,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49100,7 +49100,7 @@
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49169,8 +49169,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G768" t="n">
-        <v>1.9</v>
+        <v>21.3</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49207,14 +49212,14 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49226,13 +49231,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G769" t="n">
-        <v>21.3</v>
+        <v>4.4</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48808,14 +48808,14 @@
     <row r="762" ht="15" customHeight="1">
       <c r="A762" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6053-2024</t>
         </is>
       </c>
       <c r="B762" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -48865,14 +48865,14 @@
     <row r="763" ht="15" customHeight="1">
       <c r="A763" t="inlineStr">
         <is>
-          <t>A 6056-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B763" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -48922,14 +48922,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6053-2024</t>
+          <t>A 6056-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48986,7 +48986,7 @@
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z769"/>
+  <dimension ref="A1:Z772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48808,14 +48808,14 @@
     <row r="762" ht="15" customHeight="1">
       <c r="A762" t="inlineStr">
         <is>
-          <t>A 6053-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B762" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -48865,14 +48865,14 @@
     <row r="763" ht="15" customHeight="1">
       <c r="A763" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6056-2024</t>
         </is>
       </c>
       <c r="B763" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -48922,14 +48922,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6056-2024</t>
+          <t>A 6053-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48979,14 +48979,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49036,14 +49036,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49093,14 +49093,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49169,13 +49169,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G768" t="n">
-        <v>21.3</v>
+        <v>4.6</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49209,62 +49204,238 @@
       </c>
       <c r="R768" s="2" t="inlineStr"/>
     </row>
-    <row r="769">
+    <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G769" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H769" t="n">
+        <v>0</v>
+      </c>
+      <c r="I769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J769" t="n">
+        <v>0</v>
+      </c>
+      <c r="K769" t="n">
+        <v>0</v>
+      </c>
+      <c r="L769" t="n">
+        <v>0</v>
+      </c>
+      <c r="M769" t="n">
+        <v>0</v>
+      </c>
+      <c r="N769" t="n">
+        <v>0</v>
+      </c>
+      <c r="O769" t="n">
+        <v>0</v>
+      </c>
+      <c r="P769" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q769" t="n">
+        <v>0</v>
+      </c>
+      <c r="R769" s="2" t="inlineStr"/>
+    </row>
+    <row r="770" ht="15" customHeight="1">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>A 7224-2024</t>
+        </is>
+      </c>
+      <c r="B770" s="1" t="n">
         <v>45344</v>
       </c>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E769" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G769" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H769" t="n">
-        <v>0</v>
-      </c>
-      <c r="I769" t="n">
-        <v>0</v>
-      </c>
-      <c r="J769" t="n">
-        <v>0</v>
-      </c>
-      <c r="K769" t="n">
-        <v>0</v>
-      </c>
-      <c r="L769" t="n">
-        <v>0</v>
-      </c>
-      <c r="M769" t="n">
-        <v>0</v>
-      </c>
-      <c r="N769" t="n">
-        <v>0</v>
-      </c>
-      <c r="O769" t="n">
-        <v>0</v>
-      </c>
-      <c r="P769" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q769" t="n">
-        <v>0</v>
-      </c>
-      <c r="R769" s="2" t="inlineStr"/>
+      <c r="C770" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G770" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H770" t="n">
+        <v>0</v>
+      </c>
+      <c r="I770" t="n">
+        <v>0</v>
+      </c>
+      <c r="J770" t="n">
+        <v>0</v>
+      </c>
+      <c r="K770" t="n">
+        <v>0</v>
+      </c>
+      <c r="L770" t="n">
+        <v>0</v>
+      </c>
+      <c r="M770" t="n">
+        <v>0</v>
+      </c>
+      <c r="N770" t="n">
+        <v>0</v>
+      </c>
+      <c r="O770" t="n">
+        <v>0</v>
+      </c>
+      <c r="P770" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q770" t="n">
+        <v>0</v>
+      </c>
+      <c r="R770" s="2" t="inlineStr"/>
+    </row>
+    <row r="771" ht="15" customHeight="1">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>A 7228-2024</t>
+        </is>
+      </c>
+      <c r="B771" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C771" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G771" t="n">
+        <v>3</v>
+      </c>
+      <c r="H771" t="n">
+        <v>0</v>
+      </c>
+      <c r="I771" t="n">
+        <v>0</v>
+      </c>
+      <c r="J771" t="n">
+        <v>0</v>
+      </c>
+      <c r="K771" t="n">
+        <v>0</v>
+      </c>
+      <c r="L771" t="n">
+        <v>0</v>
+      </c>
+      <c r="M771" t="n">
+        <v>0</v>
+      </c>
+      <c r="N771" t="n">
+        <v>0</v>
+      </c>
+      <c r="O771" t="n">
+        <v>0</v>
+      </c>
+      <c r="P771" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q771" t="n">
+        <v>0</v>
+      </c>
+      <c r="R771" s="2" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>A 7233-2024</t>
+        </is>
+      </c>
+      <c r="B772" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C772" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G772" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I772" t="n">
+        <v>0</v>
+      </c>
+      <c r="J772" t="n">
+        <v>0</v>
+      </c>
+      <c r="K772" t="n">
+        <v>0</v>
+      </c>
+      <c r="L772" t="n">
+        <v>0</v>
+      </c>
+      <c r="M772" t="n">
+        <v>0</v>
+      </c>
+      <c r="N772" t="n">
+        <v>0</v>
+      </c>
+      <c r="O772" t="n">
+        <v>0</v>
+      </c>
+      <c r="P772" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q772" t="n">
+        <v>0</v>
+      </c>
+      <c r="R772" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48109,14 +48109,14 @@
     <row r="750" ht="15" customHeight="1">
       <c r="A750" t="inlineStr">
         <is>
-          <t>A 3186-2024</t>
+          <t>A 3230-2024</t>
         </is>
       </c>
       <c r="B750" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         </is>
       </c>
       <c r="G750" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -48166,14 +48166,14 @@
     <row r="751" ht="15" customHeight="1">
       <c r="A751" t="inlineStr">
         <is>
-          <t>A 3230-2024</t>
+          <t>A 3186-2024</t>
         </is>
       </c>
       <c r="B751" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         </is>
       </c>
       <c r="G751" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48689,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5920-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48708,8 +48708,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G760" t="n">
-        <v>9.9</v>
+        <v>17.8</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48746,14 +48751,14 @@
     <row r="761" ht="15" customHeight="1">
       <c r="A761" t="inlineStr">
         <is>
-          <t>A 5920-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B761" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48765,13 +48770,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G761" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49036,14 +49036,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49100,7 +49100,7 @@
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         </is>
       </c>
       <c r="G768" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49214,7 +49214,7 @@
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z772"/>
+  <dimension ref="A1:Z773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48689,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5920-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48708,13 +48708,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F760" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G760" t="n">
-        <v>17.8</v>
+        <v>9.9</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48751,14 +48746,14 @@
     <row r="761" ht="15" customHeight="1">
       <c r="A761" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5920-2024</t>
         </is>
       </c>
       <c r="B761" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48770,8 +48765,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G761" t="n">
-        <v>8.800000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -48808,14 +48808,14 @@
     <row r="762" ht="15" customHeight="1">
       <c r="A762" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6053-2024</t>
         </is>
       </c>
       <c r="B762" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48922,14 +48922,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6053-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48979,14 +48979,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49036,14 +49036,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49093,14 +49093,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         </is>
       </c>
       <c r="G768" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49214,7 +49214,7 @@
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
       </c>
       <c r="R771" s="2" t="inlineStr"/>
     </row>
-    <row r="772">
+    <row r="772" ht="15" customHeight="1">
       <c r="A772" t="inlineStr">
         <is>
           <t>A 7233-2024</t>
@@ -49390,7 +49390,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49436,6 +49436,63 @@
         <v>0</v>
       </c>
       <c r="R772" s="2" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>A 7484-2024</t>
+        </is>
+      </c>
+      <c r="B773" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="C773" s="1" t="n">
+        <v>45347</v>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G773" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H773" t="n">
+        <v>0</v>
+      </c>
+      <c r="I773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J773" t="n">
+        <v>0</v>
+      </c>
+      <c r="K773" t="n">
+        <v>0</v>
+      </c>
+      <c r="L773" t="n">
+        <v>0</v>
+      </c>
+      <c r="M773" t="n">
+        <v>0</v>
+      </c>
+      <c r="N773" t="n">
+        <v>0</v>
+      </c>
+      <c r="O773" t="n">
+        <v>0</v>
+      </c>
+      <c r="P773" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q773" t="n">
+        <v>0</v>
+      </c>
+      <c r="R773" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48689,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48753,7 +48753,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48865,14 +48865,14 @@
     <row r="763" ht="15" customHeight="1">
       <c r="A763" t="inlineStr">
         <is>
-          <t>A 6056-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B763" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -48922,14 +48922,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6056-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48979,14 +48979,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49036,14 +49036,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         </is>
       </c>
       <c r="G766" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49093,14 +49093,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49169,8 +49169,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G768" t="n">
-        <v>0.8</v>
+        <v>21.3</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49207,14 +49212,14 @@
     <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49226,13 +49231,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G769" t="n">
-        <v>21.3</v>
+        <v>1.9</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -49276,7 +49276,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45346</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>43381</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>43501</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44517</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>44945</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>44970</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45028</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>45170</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45259</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33873,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34733,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34904,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39750,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40868,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42058,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45273,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48173,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48632,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48689,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48753,7 +48753,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49093,14 +49093,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49150,14 +49150,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49169,13 +49169,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G768" t="n">
-        <v>21.3</v>
+        <v>4.4</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49212,14 +49207,14 @@
     <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49231,8 +49226,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G769" t="n">
-        <v>1.9</v>
+        <v>21.3</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -49276,7 +49276,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45346</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z773"/>
+  <dimension ref="A1:Z776"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3092,14 +3092,14 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50716-2018</t>
+          <t>A 60881-2023</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>43381</v>
+        <v>45259</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>5</v>
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3136,15 +3136,111 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8</v>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Storspov
+Lappuggla
+Björktrast
+Buskskvätta
+Rosenfink
+Svartvit flugsnappare
+Talltita
+Bivråk</t>
+        </is>
+      </c>
+      <c r="S26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 60881-2023 artfynd.xlsx", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="T26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 60881-2023 karta.png", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="V26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 60881-2023 FSC-klagomål.docx", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 60881-2023 FSC-klagomål mail.docx", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 60881-2023 tillsynsbegäran.docx", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 60881-2023 tillsynsbegäran mail.docx", "A 60881-2023")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 60881-2023 prioriterade fågelarter.docx", "A 60881-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 50716-2018</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>43381</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>6</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>7</v>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>Liten aspgelélav
 Harticka
@@ -3155,87 +3251,87 @@
 Stor aspticka</t>
         </is>
       </c>
-      <c r="S26">
+      <c r="S27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 50716-2018 artfynd.xlsx", "A 50716-2018")</f>
         <v/>
       </c>
-      <c r="T26">
+      <c r="T27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 50716-2018 karta.png", "A 50716-2018")</f>
         <v/>
       </c>
-      <c r="V26">
+      <c r="V27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 50716-2018 FSC-klagomål.docx", "A 50716-2018")</f>
         <v/>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 50716-2018 FSC-klagomål mail.docx", "A 50716-2018")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 50716-2018 tillsynsbegäran.docx", "A 50716-2018")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 50716-2018 tillsynsbegäran mail.docx", "A 50716-2018")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 8023-2019</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B28" s="1" t="n">
         <v>43501</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="C28" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>1.7</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q28" t="n">
         <v>7</v>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Garnlav
@@ -3246,91 +3342,91 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S27">
+      <c r="S28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 8023-2019 artfynd.xlsx", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="T27">
+      <c r="T28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 8023-2019 karta.png", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="U27">
+      <c r="U28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 8023-2019 karta knärot.png", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="V27">
+      <c r="V28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 8023-2019 FSC-klagomål.docx", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 8023-2019 FSC-klagomål mail.docx", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 8023-2019 tillsynsbegäran.docx", "A 8023-2019")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 8023-2019 tillsynsbegäran mail.docx", "A 8023-2019")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 65938-2021</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B29" s="1" t="n">
         <v>44517</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="C29" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>4.4</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P29" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q29" t="n">
         <v>7</v>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Sprickporing
@@ -3341,95 +3437,95 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="S28">
+      <c r="S29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 65938-2021 artfynd.xlsx", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="T28">
+      <c r="T29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 65938-2021 karta.png", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="U28">
+      <c r="U29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 65938-2021 karta knärot.png", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="V28">
+      <c r="V29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 65938-2021 FSC-klagomål.docx", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 65938-2021 FSC-klagomål mail.docx", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 65938-2021 tillsynsbegäran.docx", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 65938-2021 tillsynsbegäran mail.docx", "A 65938-2021")</f>
         <v/>
       </c>
-      <c r="Z28">
+      <c r="Z29">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 65938-2021 prioriterade fågelarter.docx", "A 65938-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 3341-2023</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B30" s="1" t="n">
         <v>44945</v>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="C30" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
         <v>12.3</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>3</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>7</v>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Grantaggsvamp
 Granticka
@@ -3440,87 +3536,87 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S29">
+      <c r="S30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 3341-2023 artfynd.xlsx", "A 3341-2023")</f>
         <v/>
       </c>
-      <c r="T29">
+      <c r="T30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 3341-2023 karta.png", "A 3341-2023")</f>
         <v/>
       </c>
-      <c r="V29">
+      <c r="V30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 3341-2023 FSC-klagomål.docx", "A 3341-2023")</f>
         <v/>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 3341-2023 FSC-klagomål mail.docx", "A 3341-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 3341-2023 tillsynsbegäran.docx", "A 3341-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 3341-2023 tillsynsbegäran mail.docx", "A 3341-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 8120-2023</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B31" s="1" t="n">
         <v>44970</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="C31" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H31" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>3</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>4</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P31" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q31" t="n">
         <v>7</v>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Garnlav
@@ -3531,96 +3627,96 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="S30">
+      <c r="S31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 8120-2023 artfynd.xlsx", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="T30">
+      <c r="T31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 8120-2023 karta.png", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="U30">
+      <c r="U31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/knärot/A 8120-2023 karta knärot.png", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="V30">
+      <c r="V31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 8120-2023 FSC-klagomål.docx", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 8120-2023 FSC-klagomål mail.docx", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 8120-2023 tillsynsbegäran.docx", "A 8120-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 8120-2023 tillsynsbegäran mail.docx", "A 8120-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 16369-2023</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B32" s="1" t="n">
         <v>45028</v>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="C32" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>4.6</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>4</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>7</v>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Rynkskinn
 Flattoppad klubbsvamp
@@ -3631,87 +3727,87 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S31">
+      <c r="S32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 16369-2023 artfynd.xlsx", "A 16369-2023")</f>
         <v/>
       </c>
-      <c r="T31">
+      <c r="T32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 16369-2023 karta.png", "A 16369-2023")</f>
         <v/>
       </c>
-      <c r="V31">
+      <c r="V32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 16369-2023 FSC-klagomål.docx", "A 16369-2023")</f>
         <v/>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 16369-2023 FSC-klagomål mail.docx", "A 16369-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 16369-2023 tillsynsbegäran.docx", "A 16369-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 16369-2023 tillsynsbegäran mail.docx", "A 16369-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 16688-2023</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B33" s="1" t="n">
         <v>45028</v>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="C33" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
         <v>5</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>3</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>7</v>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Trolldruvemätare
 Grantaggsvamp
@@ -3722,92 +3818,92 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S32">
+      <c r="S33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 16688-2023 artfynd.xlsx", "A 16688-2023")</f>
         <v/>
       </c>
-      <c r="T32">
+      <c r="T33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 16688-2023 karta.png", "A 16688-2023")</f>
         <v/>
       </c>
-      <c r="V32">
+      <c r="V33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 16688-2023 FSC-klagomål.docx", "A 16688-2023")</f>
         <v/>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 16688-2023 FSC-klagomål mail.docx", "A 16688-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 16688-2023 tillsynsbegäran.docx", "A 16688-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 16688-2023 tillsynsbegäran mail.docx", "A 16688-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 40777-2023</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B34" s="1" t="n">
         <v>45170</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C34" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G34" t="n">
         <v>16.4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>4</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>5</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>7</v>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Doftticka
 Lunglav
@@ -3818,123 +3914,28 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="S33">
+      <c r="S34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 40777-2023 artfynd.xlsx", "A 40777-2023")</f>
         <v/>
       </c>
-      <c r="T33">
+      <c r="T34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 40777-2023 karta.png", "A 40777-2023")</f>
         <v/>
       </c>
-      <c r="V33">
+      <c r="V34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 40777-2023 FSC-klagomål.docx", "A 40777-2023")</f>
         <v/>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 40777-2023 FSC-klagomål mail.docx", "A 40777-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 40777-2023 tillsynsbegäran.docx", "A 40777-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 40777-2023 tillsynsbegäran mail.docx", "A 40777-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 60881-2023</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>45259</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>JÄMTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ÖSTERSUND</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>7</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>7</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>7</v>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Storspov
-Lappuggla
-Björktrast
-Buskskvätta
-Rosenfink
-Svartvit flugsnappare
-Talltita</t>
-        </is>
-      </c>
-      <c r="S34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/artfynd/A 60881-2023 artfynd.xlsx", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="T34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/kartor/A 60881-2023 karta.png", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="V34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomål/A 60881-2023 FSC-klagomål.docx", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/klagomålsmail/A 60881-2023 FSC-klagomål mail.docx", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsyn/A 60881-2023 tillsynsbegäran.docx", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/tillsynsmail/A 60881-2023 tillsynsbegäran mail.docx", "A 60881-2023")</f>
-        <v/>
-      </c>
-      <c r="Z34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2380/fåglar/A 60881-2023 prioriterade fågelarter.docx", "A 60881-2023")</f>
         <v/>
       </c>
     </row>
@@ -3948,7 +3949,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4039,7 +4040,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,7 +4134,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4227,7 +4228,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4325,7 +4326,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4420,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,7 +4514,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4607,7 +4608,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4701,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,7 +4795,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4883,7 +4884,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4971,7 +4972,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,7 +5060,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,7 +5157,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,7 +5254,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5340,7 +5341,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5432,7 +5433,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5524,7 +5525,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5611,7 +5612,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5702,7 +5703,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5798,7 +5799,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5885,7 +5886,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5980,7 +5981,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6071,7 +6072,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,7 +6159,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6245,7 +6246,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,7 +6337,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6432,7 +6433,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,7 +6525,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6615,7 +6616,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6701,7 +6702,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6787,7 +6788,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6878,7 +6879,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6964,7 +6965,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7050,7 +7051,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7140,7 +7141,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7231,7 +7232,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7321,7 +7322,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7407,7 +7408,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7493,7 +7494,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7579,7 +7580,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7665,7 +7666,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7751,7 +7752,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7837,7 +7838,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7928,7 +7929,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8014,7 +8015,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8104,7 +8105,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8190,7 +8191,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8276,7 +8277,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8362,7 +8363,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8452,7 +8453,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8537,7 +8538,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8622,7 +8623,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8707,7 +8708,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8796,7 +8797,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8881,7 +8882,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8966,7 +8967,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9051,7 +9052,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9136,7 +9137,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9221,7 +9222,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9311,7 +9312,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9400,7 +9401,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9485,7 +9486,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9575,7 +9576,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9665,7 +9666,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9750,7 +9751,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9840,7 +9841,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9930,7 +9931,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10024,7 +10025,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10113,7 +10114,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10203,7 +10204,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10293,7 +10294,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10383,7 +10384,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10473,7 +10474,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10559,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10649,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10733,7 +10734,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10818,7 +10819,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10903,7 +10904,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10988,7 +10989,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11073,7 +11074,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11167,7 +11168,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11252,7 +11253,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11337,7 +11338,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11394,7 +11395,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11451,7 +11452,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11508,7 +11509,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11565,7 +11566,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11622,7 +11623,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11679,7 +11680,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11741,7 +11742,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11798,7 +11799,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11855,7 +11856,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11912,7 +11913,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11969,7 +11970,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12026,7 +12027,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12083,7 +12084,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12140,7 +12141,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12202,7 +12203,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12264,7 +12265,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12321,7 +12322,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12378,7 +12379,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12435,7 +12436,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12492,7 +12493,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12549,7 +12550,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12606,7 +12607,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12663,7 +12664,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12720,7 +12721,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12777,7 +12778,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12834,7 +12835,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12891,7 +12892,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12948,7 +12949,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13005,7 +13006,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13062,7 +13063,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13119,7 +13120,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13176,7 +13177,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13233,7 +13234,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13290,7 +13291,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13347,7 +13348,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13404,7 +13405,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13461,7 +13462,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13518,7 +13519,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13575,7 +13576,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13632,7 +13633,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13689,7 +13690,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13746,7 +13747,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13803,7 +13804,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13860,7 +13861,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13917,7 +13918,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13974,7 +13975,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14031,7 +14032,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14088,7 +14089,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14145,7 +14146,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14202,7 +14203,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14259,7 +14260,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14316,7 +14317,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14373,7 +14374,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14430,7 +14431,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14487,7 +14488,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14549,7 +14550,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14606,7 +14607,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14663,7 +14664,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14720,7 +14721,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14782,7 +14783,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14839,7 +14840,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14896,7 +14897,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14953,7 +14954,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15010,7 +15011,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15067,7 +15068,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15124,7 +15125,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15181,7 +15182,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15243,7 +15244,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15305,7 +15306,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15362,7 +15363,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15419,7 +15420,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15476,7 +15477,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15538,7 +15539,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15595,7 +15596,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15657,7 +15658,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15714,7 +15715,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15771,7 +15772,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15828,7 +15829,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15885,7 +15886,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15942,7 +15943,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15999,7 +16000,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16056,7 +16057,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16113,7 +16114,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16175,7 +16176,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16232,7 +16233,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16294,7 +16295,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16356,7 +16357,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16413,7 +16414,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16470,7 +16471,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16527,7 +16528,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16589,7 +16590,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16651,7 +16652,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16713,7 +16714,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16770,7 +16771,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16832,7 +16833,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16889,7 +16890,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16951,7 +16952,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17008,7 +17009,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17065,7 +17066,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17127,7 +17128,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17184,7 +17185,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17241,7 +17242,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17298,7 +17299,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17360,7 +17361,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17417,7 +17418,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17479,7 +17480,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17536,7 +17537,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17593,7 +17594,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17650,7 +17651,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17707,7 +17708,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17764,7 +17765,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17821,7 +17822,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17878,7 +17879,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17935,7 +17936,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17992,7 +17993,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18054,7 +18055,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18111,7 +18112,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18168,7 +18169,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18225,7 +18226,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18282,7 +18283,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18339,7 +18340,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18396,7 +18397,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18453,7 +18454,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18510,7 +18511,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18567,7 +18568,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18624,7 +18625,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18681,7 +18682,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18738,7 +18739,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18795,7 +18796,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18852,7 +18853,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18909,7 +18910,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18966,7 +18967,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19023,7 +19024,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19080,7 +19081,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19137,7 +19138,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19194,7 +19195,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19251,7 +19252,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19308,7 +19309,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19370,7 +19371,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19427,7 +19428,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19484,7 +19485,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19541,7 +19542,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19598,7 +19599,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19655,7 +19656,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19712,7 +19713,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19769,7 +19770,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19826,7 +19827,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19883,7 +19884,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19940,7 +19941,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19997,7 +19998,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20054,7 +20055,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20111,7 +20112,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20168,7 +20169,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20225,7 +20226,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20287,7 +20288,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20344,7 +20345,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20401,7 +20402,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20463,7 +20464,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20520,7 +20521,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20577,7 +20578,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20639,7 +20640,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20701,7 +20702,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20758,7 +20759,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20820,7 +20821,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20882,7 +20883,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20944,7 +20945,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21001,7 +21002,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21063,7 +21064,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21125,7 +21126,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21187,7 +21188,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21249,7 +21250,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21311,7 +21312,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21368,7 +21369,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21425,7 +21426,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21482,7 +21483,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21539,7 +21540,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21601,7 +21602,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21658,7 +21659,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21715,7 +21716,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21772,7 +21773,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21829,7 +21830,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21886,7 +21887,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21948,7 +21949,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22010,7 +22011,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22072,7 +22073,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22134,7 +22135,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22196,7 +22197,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22258,7 +22259,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22320,7 +22321,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22377,7 +22378,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22439,7 +22440,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22501,7 +22502,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22563,7 +22564,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22625,7 +22626,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22687,7 +22688,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22744,7 +22745,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22801,7 +22802,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22858,7 +22859,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22915,7 +22916,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22972,7 +22973,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23029,7 +23030,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23086,7 +23087,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23143,7 +23144,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23200,7 +23201,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23257,7 +23258,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23314,7 +23315,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23371,7 +23372,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23433,7 +23434,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23490,7 +23491,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23547,7 +23548,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23604,7 +23605,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23661,7 +23662,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23718,7 +23719,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23775,7 +23776,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23832,7 +23833,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23889,7 +23890,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23951,7 +23952,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24008,7 +24009,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24065,7 +24066,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24122,7 +24123,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24179,7 +24180,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24236,7 +24237,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24293,7 +24294,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24350,7 +24351,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24407,7 +24408,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24464,7 +24465,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24521,7 +24522,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24578,7 +24579,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24635,7 +24636,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24692,7 +24693,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24749,7 +24750,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24806,7 +24807,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24863,7 +24864,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24920,7 +24921,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24977,7 +24978,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25034,7 +25035,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25091,7 +25092,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25148,7 +25149,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25205,7 +25206,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25262,7 +25263,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25319,7 +25320,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25376,7 +25377,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25433,7 +25434,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25490,7 +25491,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25547,7 +25548,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25604,7 +25605,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25661,7 +25662,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25718,7 +25719,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25775,7 +25776,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25832,7 +25833,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25889,7 +25890,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25951,7 +25952,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26008,7 +26009,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26065,7 +26066,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26122,7 +26123,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26179,7 +26180,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26236,7 +26237,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26293,7 +26294,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26350,7 +26351,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26407,7 +26408,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26464,7 +26465,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26521,7 +26522,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26578,7 +26579,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26635,7 +26636,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26692,7 +26693,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26754,7 +26755,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26811,7 +26812,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26868,7 +26869,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26925,7 +26926,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26987,7 +26988,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27049,7 +27050,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27106,7 +27107,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27163,7 +27164,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27220,7 +27221,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27277,7 +27278,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27334,7 +27335,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27391,7 +27392,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27448,7 +27449,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27505,7 +27506,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27562,7 +27563,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27619,7 +27620,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27676,7 +27677,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27733,7 +27734,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27790,7 +27791,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27847,7 +27848,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27904,7 +27905,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27961,7 +27962,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28018,7 +28019,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28075,7 +28076,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28132,7 +28133,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28189,7 +28190,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28251,7 +28252,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28308,7 +28309,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28365,7 +28366,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28422,7 +28423,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28479,7 +28480,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28536,7 +28537,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28593,7 +28594,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28650,7 +28651,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28707,7 +28708,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28764,7 +28765,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28821,7 +28822,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28878,7 +28879,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28935,7 +28936,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28992,7 +28993,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29049,7 +29050,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29106,7 +29107,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29168,7 +29169,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29225,7 +29226,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29282,7 +29283,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29339,7 +29340,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29396,7 +29397,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29453,7 +29454,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29510,7 +29511,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29567,7 +29568,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29624,7 +29625,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29681,7 +29682,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29738,7 +29739,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29795,7 +29796,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29852,7 +29853,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29914,7 +29915,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29971,7 +29972,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30028,7 +30029,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30085,7 +30086,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30142,7 +30143,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30199,7 +30200,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30256,7 +30257,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30318,7 +30319,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30375,7 +30376,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30437,7 +30438,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30499,7 +30500,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30556,7 +30557,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30613,7 +30614,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30670,7 +30671,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30732,7 +30733,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30814,7 +30815,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30876,7 +30877,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30933,7 +30934,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30990,7 +30991,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31047,7 +31048,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31109,7 +31110,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31171,7 +31172,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31228,7 +31229,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31285,7 +31286,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31342,7 +31343,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31399,7 +31400,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31456,7 +31457,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31513,7 +31514,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31570,7 +31571,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31627,7 +31628,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31689,7 +31690,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31746,7 +31747,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31803,7 +31804,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31865,7 +31866,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31922,7 +31923,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31979,7 +31980,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32036,7 +32037,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32093,7 +32094,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32150,7 +32151,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32207,7 +32208,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32264,7 +32265,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32326,7 +32327,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32388,7 +32389,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32445,7 +32446,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32507,7 +32508,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32569,7 +32570,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32626,7 +32627,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32683,7 +32684,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32740,7 +32741,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32797,7 +32798,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32859,7 +32860,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32916,7 +32917,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32978,7 +32979,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33035,7 +33036,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33097,7 +33098,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33154,7 +33155,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33216,7 +33217,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33278,7 +33279,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33335,7 +33336,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33397,7 +33398,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33454,7 +33455,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33511,7 +33512,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33568,7 +33569,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33630,7 +33631,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33692,7 +33693,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33754,7 +33755,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33816,7 +33817,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33873,7 +33874,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33935,7 +33936,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33992,7 +33993,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34049,7 +34050,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34106,7 +34107,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34163,7 +34164,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34220,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34277,7 +34278,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34334,7 +34335,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34391,7 +34392,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34448,7 +34449,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34505,7 +34506,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34562,7 +34563,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34619,7 +34620,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34676,7 +34677,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34733,7 +34734,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34790,7 +34791,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34847,7 +34848,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34904,7 +34905,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34961,7 +34962,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35018,7 +35019,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35075,7 +35076,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35132,7 +35133,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35189,7 +35190,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35246,7 +35247,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35303,7 +35304,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35360,7 +35361,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35417,7 +35418,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35474,7 +35475,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35531,7 +35532,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35588,7 +35589,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35645,7 +35646,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35702,7 +35703,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35764,7 +35765,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35821,7 +35822,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35878,7 +35879,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35935,7 +35936,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35997,7 +35998,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36059,7 +36060,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36116,7 +36117,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36178,7 +36179,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36235,7 +36236,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36292,7 +36293,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36354,7 +36355,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36416,7 +36417,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36478,7 +36479,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36540,7 +36541,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36602,7 +36603,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36664,7 +36665,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36726,7 +36727,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36783,7 +36784,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36840,7 +36841,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36902,7 +36903,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36959,7 +36960,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37016,7 +37017,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37073,7 +37074,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37130,7 +37131,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37187,7 +37188,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37244,7 +37245,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37301,7 +37302,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37358,7 +37359,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37420,7 +37421,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37477,7 +37478,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37534,7 +37535,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37596,7 +37597,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37653,7 +37654,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37710,7 +37711,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37772,7 +37773,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37834,7 +37835,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37891,7 +37892,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37953,7 +37954,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38015,7 +38016,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38077,7 +38078,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38134,7 +38135,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38196,7 +38197,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38253,7 +38254,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38310,7 +38311,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38372,7 +38373,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38429,7 +38430,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38491,7 +38492,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38548,7 +38549,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38605,7 +38606,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38662,7 +38663,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38719,7 +38720,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38776,7 +38777,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38833,7 +38834,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38890,7 +38891,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38947,7 +38948,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39004,7 +39005,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39061,7 +39062,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39118,7 +39119,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39175,7 +39176,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39232,7 +39233,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39289,7 +39290,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39346,7 +39347,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39403,7 +39404,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39465,7 +39466,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39522,7 +39523,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39579,7 +39580,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39636,7 +39637,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39693,7 +39694,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39750,7 +39751,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39812,7 +39813,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39869,7 +39870,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39926,7 +39927,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39983,7 +39984,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40040,7 +40041,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40097,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40159,7 +40160,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40221,7 +40222,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40278,7 +40279,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40335,7 +40336,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40397,7 +40398,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40454,7 +40455,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40516,7 +40517,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40573,7 +40574,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40630,7 +40631,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40692,7 +40693,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40754,7 +40755,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40811,7 +40812,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40868,7 +40869,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40925,7 +40926,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40987,7 +40988,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41049,7 +41050,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41106,7 +41107,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41168,7 +41169,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41225,7 +41226,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41287,7 +41288,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41349,7 +41350,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41411,7 +41412,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41468,7 +41469,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41530,7 +41531,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41587,7 +41588,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41649,7 +41650,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41711,7 +41712,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41768,7 +41769,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41830,7 +41831,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41887,7 +41888,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41944,7 +41945,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42001,7 +42002,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42058,7 +42059,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42115,7 +42116,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42172,7 +42173,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42229,7 +42230,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42291,7 +42292,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42353,7 +42354,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42410,7 +42411,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42467,7 +42468,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42524,7 +42525,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42581,7 +42582,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42638,7 +42639,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42695,7 +42696,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42752,7 +42753,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42809,7 +42810,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42866,7 +42867,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42923,7 +42924,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42980,7 +42981,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43037,7 +43038,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43094,7 +43095,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43151,7 +43152,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43208,7 +43209,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43270,7 +43271,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43332,7 +43333,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43394,7 +43395,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43451,7 +43452,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43508,7 +43509,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43565,7 +43566,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43622,7 +43623,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43679,7 +43680,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43741,7 +43742,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43803,7 +43804,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43860,7 +43861,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43917,7 +43918,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43979,7 +43980,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44036,7 +44037,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44093,7 +44094,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44155,7 +44156,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44212,7 +44213,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44274,7 +44275,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44331,7 +44332,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44388,7 +44389,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44445,7 +44446,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44502,7 +44503,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44559,7 +44560,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44621,7 +44622,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44678,7 +44679,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44740,7 +44741,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44802,7 +44803,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44864,7 +44865,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44921,7 +44922,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44983,7 +44984,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45040,7 +45041,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45102,7 +45103,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45159,7 +45160,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45216,7 +45217,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45273,7 +45274,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45330,7 +45331,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45387,7 +45388,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45444,7 +45445,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45501,7 +45502,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45558,7 +45559,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45615,7 +45616,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45672,7 +45673,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45729,7 +45730,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45786,7 +45787,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45843,7 +45844,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45900,7 +45901,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45962,7 +45963,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46019,7 +46020,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46081,7 +46082,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46138,7 +46139,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46195,7 +46196,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46257,7 +46258,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46314,7 +46315,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46376,7 +46377,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46438,7 +46439,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46500,7 +46501,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46562,7 +46563,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46619,7 +46620,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46676,7 +46677,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46733,7 +46734,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46790,7 +46791,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46847,7 +46848,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46909,7 +46910,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46966,7 +46967,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47023,7 +47024,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47080,7 +47081,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47137,7 +47138,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47194,7 +47195,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47251,7 +47252,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47313,7 +47314,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47370,7 +47371,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47427,7 +47428,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47484,7 +47485,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47541,7 +47542,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47598,7 +47599,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47655,7 +47656,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47712,7 +47713,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47769,7 +47770,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47826,7 +47827,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47883,7 +47884,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47945,7 +47946,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48002,7 +48003,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48059,7 +48060,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48116,7 +48117,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48173,7 +48174,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48230,7 +48231,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48287,7 +48288,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48344,7 +48345,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48401,7 +48402,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48463,7 +48464,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48525,7 +48526,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48582,7 +48583,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48632,14 +48633,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48652,7 +48653,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48689,14 +48690,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48709,7 +48710,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48753,7 +48754,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48808,14 +48809,14 @@
     <row r="762" ht="15" customHeight="1">
       <c r="A762" t="inlineStr">
         <is>
-          <t>A 6053-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B762" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48828,7 +48829,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -48865,14 +48866,14 @@
     <row r="763" ht="15" customHeight="1">
       <c r="A763" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6056-2024</t>
         </is>
       </c>
       <c r="B763" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48885,7 +48886,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -48922,14 +48923,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6056-2024</t>
+          <t>A 6053-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48942,7 +48943,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48986,7 +48987,7 @@
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49043,7 +49044,7 @@
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49093,14 +49094,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49113,7 +49114,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49150,14 +49151,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49169,8 +49170,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G768" t="n">
-        <v>4.4</v>
+        <v>21.3</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49207,14 +49213,14 @@
     <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49226,13 +49232,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G769" t="n">
-        <v>21.3</v>
+        <v>1.9</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -49276,7 +49277,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49333,7 +49334,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49390,7 +49391,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49437,7 +49438,7 @@
       </c>
       <c r="R772" s="2" t="inlineStr"/>
     </row>
-    <row r="773">
+    <row r="773" ht="15" customHeight="1">
       <c r="A773" t="inlineStr">
         <is>
           <t>A 7484-2024</t>
@@ -49447,7 +49448,7 @@
         <v>45346</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49493,6 +49494,192 @@
         <v>0</v>
       </c>
       <c r="R773" s="2" t="inlineStr"/>
+    </row>
+    <row r="774" ht="15" customHeight="1">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>A 7710-2024</t>
+        </is>
+      </c>
+      <c r="B774" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C774" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G774" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H774" t="n">
+        <v>0</v>
+      </c>
+      <c r="I774" t="n">
+        <v>0</v>
+      </c>
+      <c r="J774" t="n">
+        <v>0</v>
+      </c>
+      <c r="K774" t="n">
+        <v>0</v>
+      </c>
+      <c r="L774" t="n">
+        <v>0</v>
+      </c>
+      <c r="M774" t="n">
+        <v>0</v>
+      </c>
+      <c r="N774" t="n">
+        <v>0</v>
+      </c>
+      <c r="O774" t="n">
+        <v>0</v>
+      </c>
+      <c r="P774" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q774" t="n">
+        <v>0</v>
+      </c>
+      <c r="R774" s="2" t="inlineStr"/>
+    </row>
+    <row r="775" ht="15" customHeight="1">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>A 7717-2024</t>
+        </is>
+      </c>
+      <c r="B775" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C775" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G775" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" t="n">
+        <v>0</v>
+      </c>
+      <c r="J775" t="n">
+        <v>0</v>
+      </c>
+      <c r="K775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L775" t="n">
+        <v>0</v>
+      </c>
+      <c r="M775" t="n">
+        <v>0</v>
+      </c>
+      <c r="N775" t="n">
+        <v>0</v>
+      </c>
+      <c r="O775" t="n">
+        <v>0</v>
+      </c>
+      <c r="P775" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q775" t="n">
+        <v>0</v>
+      </c>
+      <c r="R775" s="2" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>A 7698-2024</t>
+        </is>
+      </c>
+      <c r="B776" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C776" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>ÖSTERSUND</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G776" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H776" t="n">
+        <v>0</v>
+      </c>
+      <c r="I776" t="n">
+        <v>0</v>
+      </c>
+      <c r="J776" t="n">
+        <v>0</v>
+      </c>
+      <c r="K776" t="n">
+        <v>0</v>
+      </c>
+      <c r="L776" t="n">
+        <v>0</v>
+      </c>
+      <c r="M776" t="n">
+        <v>0</v>
+      </c>
+      <c r="N776" t="n">
+        <v>0</v>
+      </c>
+      <c r="O776" t="n">
+        <v>0</v>
+      </c>
+      <c r="P776" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q776" t="n">
+        <v>0</v>
+      </c>
+      <c r="R776" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45259</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>43381</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>43501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44517</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>44945</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45028</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45170</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48809,14 +48809,14 @@
     <row r="762" ht="15" customHeight="1">
       <c r="A762" t="inlineStr">
         <is>
-          <t>A 6048-2024</t>
+          <t>A 6053-2024</t>
         </is>
       </c>
       <c r="B762" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         </is>
       </c>
       <c r="G762" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -48866,14 +48866,14 @@
     <row r="763" ht="15" customHeight="1">
       <c r="A763" t="inlineStr">
         <is>
-          <t>A 6056-2024</t>
+          <t>A 6048-2024</t>
         </is>
       </c>
       <c r="B763" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         </is>
       </c>
       <c r="G763" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -48923,14 +48923,14 @@
     <row r="764" ht="15" customHeight="1">
       <c r="A764" t="inlineStr">
         <is>
-          <t>A 6053-2024</t>
+          <t>A 6056-2024</t>
         </is>
       </c>
       <c r="B764" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="G764" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -48980,14 +48980,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49037,14 +49037,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,8 +49056,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G766" t="n">
-        <v>4.6</v>
+        <v>21.3</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49094,14 +49099,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49114,7 +49119,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49151,14 +49156,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49170,13 +49175,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F768" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G768" t="n">
-        <v>21.3</v>
+        <v>4.6</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49213,14 +49213,14 @@
     <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         </is>
       </c>
       <c r="G769" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -49277,7 +49277,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45346</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49498,14 +49498,14 @@
     <row r="774" ht="15" customHeight="1">
       <c r="A774" t="inlineStr">
         <is>
-          <t>A 7710-2024</t>
+          <t>A 7698-2024</t>
         </is>
       </c>
       <c r="B774" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         </is>
       </c>
       <c r="G774" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -49560,14 +49560,14 @@
     <row r="775" ht="15" customHeight="1">
       <c r="A775" t="inlineStr">
         <is>
-          <t>A 7717-2024</t>
+          <t>A 7710-2024</t>
         </is>
       </c>
       <c r="B775" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         </is>
       </c>
       <c r="G775" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -49622,14 +49622,14 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>A 7698-2024</t>
+          <t>A 7717-2024</t>
         </is>
       </c>
       <c r="B776" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         </is>
       </c>
       <c r="G776" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H776" t="n">
         <v>0</v>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45259</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>43381</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>43501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44517</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>44945</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45028</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45170</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45223</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45225</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45231</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45231</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45231</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45232</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45233</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45233</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45233</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45233</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45236</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>45236</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45236</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45237</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45237</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45237</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45237</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45239</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45238</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45239</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45239</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45239</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45243</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45243</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45244</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45245</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45247</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45247</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45217,7 +45217,7 @@
         <v>45247</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45250</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45253</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45253</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45254</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45254</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45256</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45257</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45258</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45260</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45260</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45261</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45261</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45261</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45264</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45264</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45265</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45265</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>45271</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45271</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45272</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45273</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45273</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45273</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45277</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45277</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45279</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45279</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45280</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45280</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45281</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45282</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45282</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45298</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45298</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45300</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45300</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45302</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45306</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45306</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45307</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45309</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45313</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45313</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45314</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45315</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45315</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45316</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45316</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45316</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45320</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>45321</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45323</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>45324</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45328</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45331</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48633,14 +48633,14 @@
     <row r="759" ht="15" customHeight="1">
       <c r="A759" t="inlineStr">
         <is>
-          <t>A 5779-2024</t>
+          <t>A 5781-2024</t>
         </is>
       </c>
       <c r="B759" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         </is>
       </c>
       <c r="G759" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -48690,14 +48690,14 @@
     <row r="760" ht="15" customHeight="1">
       <c r="A760" t="inlineStr">
         <is>
-          <t>A 5781-2024</t>
+          <t>A 5779-2024</t>
         </is>
       </c>
       <c r="B760" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         </is>
       </c>
       <c r="G760" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H760" t="n">
         <v>0</v>
@@ -48754,7 +48754,7 @@
         <v>45335</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45336</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45336</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45336</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48980,14 +48980,14 @@
     <row r="765" ht="15" customHeight="1">
       <c r="A765" t="inlineStr">
         <is>
-          <t>A 6353-2024</t>
+          <t>A 6351-2024</t>
         </is>
       </c>
       <c r="B765" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         </is>
       </c>
       <c r="G765" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -49037,14 +49037,14 @@
     <row r="766" ht="15" customHeight="1">
       <c r="A766" t="inlineStr">
         <is>
-          <t>A 6481-2024</t>
+          <t>A 6376-2024</t>
         </is>
       </c>
       <c r="B766" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49056,13 +49056,8 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G766" t="n">
-        <v>21.3</v>
+        <v>4.6</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -49099,14 +49094,14 @@
     <row r="767" ht="15" customHeight="1">
       <c r="A767" t="inlineStr">
         <is>
-          <t>A 6351-2024</t>
+          <t>A 6402-2024</t>
         </is>
       </c>
       <c r="B767" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49119,7 +49114,7 @@
         </is>
       </c>
       <c r="G767" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -49156,14 +49151,14 @@
     <row r="768" ht="15" customHeight="1">
       <c r="A768" t="inlineStr">
         <is>
-          <t>A 6376-2024</t>
+          <t>A 6353-2024</t>
         </is>
       </c>
       <c r="B768" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49176,7 +49171,7 @@
         </is>
       </c>
       <c r="G768" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -49213,14 +49208,14 @@
     <row r="769" ht="15" customHeight="1">
       <c r="A769" t="inlineStr">
         <is>
-          <t>A 6402-2024</t>
+          <t>A 6481-2024</t>
         </is>
       </c>
       <c r="B769" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49232,8 +49227,13 @@
           <t>ÖSTERSUND</t>
         </is>
       </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G769" t="n">
-        <v>4.4</v>
+        <v>21.3</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -49277,7 +49277,7 @@
         <v>45344</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45344</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45344</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45346</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45349</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49560,14 +49560,14 @@
     <row r="775" ht="15" customHeight="1">
       <c r="A775" t="inlineStr">
         <is>
-          <t>A 7710-2024</t>
+          <t>A 7717-2024</t>
         </is>
       </c>
       <c r="B775" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         </is>
       </c>
       <c r="G775" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -49622,14 +49622,14 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>A 7717-2024</t>
+          <t>A 7710-2024</t>
         </is>
       </c>
       <c r="B776" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         </is>
       </c>
       <c r="G776" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H776" t="n">
         <v>0</v>

--- a/Översikt ÖSTERSUND.xlsx
+++ b/Översikt ÖSTERSUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z776"/>
+  <dimension ref="A1:Z777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
         <v>44585</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>45155</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>43739</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>43782</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>44344</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>43813</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44817</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>45112</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>44886</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>44851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>44945</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45121</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>44642</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>44890</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>44106</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44706</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44918</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45099</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>43719</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44971</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44578</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44701</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45063</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45259</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>43381</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>43501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44517</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>44945</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45028</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45028</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>45170</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45260</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44270</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44337</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>44356</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>44929</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45254</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44742</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44851</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44889</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44750</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44904</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>44945</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45237</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>43592</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>43607</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>43672</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>43784</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44242</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44473</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44750</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44817</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44904</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44956</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45049</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45063</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>45187</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45198</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>45215</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>43378</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>43446</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43656</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44361</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44363</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>44441</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44508</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44904</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44908</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         <v>44911</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45044</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45161</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45189</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45223</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45233</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45246</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45278</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45321</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>43636</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>43768</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>43784</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43893</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44047</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44165</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44272</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44298</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44343</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44368</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44441</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44476</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44491</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>44617</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>44694</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44742</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>44742</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44785</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>44838</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44838</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44844</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44890</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>44900</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44908</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45096</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45120</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45217</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>45233</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45244</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45279</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45280</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45316</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43314</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43314</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43321</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43321</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43332</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43336</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>43364</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>43364</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>43371</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>43371</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43371</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43371</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43381</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43395</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>43398</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>43398</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>43399</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>43402</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>43411</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>43412</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>43419</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>43423</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>43425</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>43426</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>43439</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>43440</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>43448</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43451</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43452</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>43454</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>43454</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>43455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43472</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43472</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43475</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43476</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43478</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43489</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43489</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43494</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43494</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43494</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43495</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43495</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43503</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43514</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43530</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43542</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43549</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43550</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43571</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43581</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43581</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>43584</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>43584</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>43594</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>43595</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>43600</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>43619</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>43619</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>43619</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>43620</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>43621</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>43635</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>43637</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>43636</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>43640</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>43640</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>43650</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>43651</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>43654</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>43654</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>43655</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>43656</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>43656</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>43657</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>43670</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>43676</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>43684</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>43686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>43699</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>43703</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>43703</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>43718</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>43724</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>43725</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>43727</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>43732</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>43732</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>43733</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>43735</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>43738</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>43738</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>43747</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>43748</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>43749</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>43752</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>43762</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>43768</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>43770</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>43770</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>43773</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>43776</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>43777</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>43781</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>43781</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>43784</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43794</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43802</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43805</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43809</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43809</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43817</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43838</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43840</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43840</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43840</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>43861</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>43864</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>43864</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>43865</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>43871</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>43871</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>43875</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>43893</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>43895</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>43901</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>43906</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>43909</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>43910</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>43917</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>43928</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>43930</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>43936</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>43943</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>43944</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>43969</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>43969</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>43970</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>43970</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>43978</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>43986</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>43992</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44000</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>44004</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44005</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44004</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>44008</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44027</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>44035</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>44055</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44057</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>44072</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>44076</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44078</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44077</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>44077</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>44082</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44090</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44106</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44106</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44106</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44110</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44113</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44118</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44118</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44118</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44123</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>44125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44133</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44137</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44137</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44137</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44140</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>44140</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44141</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>44141</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44151</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44152</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44162</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>44173</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44174</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>44174</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44174</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44180</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44186</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44187</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44200</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44200</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44208</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44214</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44229</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44236</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44238</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>44258</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44259</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>44259</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44270</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44270</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>44278</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>44298</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>44298</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44299</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44312</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>44314</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>44316</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>44320</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>44322</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>44323</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>44328</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>44335</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>44336</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44340</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>44340</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44347</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>44347</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44349</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44349</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44362</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44362</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44368</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>44375</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44375</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44375</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>44375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44378</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44383</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44385</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44405</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44410</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44410</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44414</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>44418</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44425</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44427</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44428</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44430</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44432</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>44434</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>44434</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>44434</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44441</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44441</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>44441</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44453</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44466</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44475</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44501</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44510</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44511</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44515</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44516</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44517</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44522</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>44524</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44524</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44529</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>44533</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>44537</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44537</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44539</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44540</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44540</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44540</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>44540</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44544</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44547</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>44550</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>44550</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>44553</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>44553</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44561</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>44564</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44566</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44566</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44579</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44580</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>44581</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44581</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44595</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44601</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44607</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>44609</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44609</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44614</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44634</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>44635</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44637</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44637</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>44642</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>44643</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44655</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44655</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>44655</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44665</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44665</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44680</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44681</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44680</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44690</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44702</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44703</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44706</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>44711</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44711</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44711</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>44721</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44721</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44721</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44722</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>44723</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>44740</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>44742</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>44743</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44742</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44742</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44743</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>44750</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>44750</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>44755</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>44755</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>44758</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44790</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>44790</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44790</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44790</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44790</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44799</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44817</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44819</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44820</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>44837</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44838</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>44840</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>44840</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44845</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>44851</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44853</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>44852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>44852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>44861</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>44867</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>44868</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>44873</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44875</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44875</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44875</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44875</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44879</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44879</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44880</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>44883</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>44883</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44886</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44886</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44886</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>44887</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44887</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44889</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>44894</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44904</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>44907</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>44908</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44910</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>44909</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44911</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44911</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44911</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44911</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>44911</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>44911</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44911</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44911</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44911</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>44911</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44911</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44911</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44914</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44916</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44918</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>44918</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>44922</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44922</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44922</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44922</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>44927</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>44928</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>44928</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>44936</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44937</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44943</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44949</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44949</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>44950</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>44952</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>44952</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>44952</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44954</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44953</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44956</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>44957</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>44963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>44965</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44970</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44977</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>44978</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44986</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44986</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>44986</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>44986</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44986</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44993</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45000</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45002</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45002</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45002</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45004</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45008</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45012</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45012</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45022</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45028</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45028</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45035</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45049</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45050</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45057</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45058</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45057</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45058</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45058</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45058</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45077</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45082</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45084</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45089</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45089</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45089</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45089</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>45089</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>45090</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>45091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45092</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45094</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45096</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45096</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45096</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45098</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45099</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45099</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45099</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45099</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45099</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45099</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45103</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45106</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45107</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45117</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45117</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45117</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45118</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45118</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45121</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45140</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45141</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45149</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40336,7 +40336,7 @@
         <v>45154</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>45159</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45159</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45161</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>45163</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45166</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45167</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45167</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45167</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45168</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45169</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45170</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45170</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45171</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>45174</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45176</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45177</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45177</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45176</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         <v>45178</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45181</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41588,7 +41588,7 @@
         <v>45181</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45181</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45182</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45183</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>45183</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45188</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45188</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45189</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45190</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45190</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45197</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45198</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45198</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>45201</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>45202</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>45203</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45210</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45211</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45215</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45217</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45218</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45222</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45223</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43209,7 +43209,7 @@
         <v>45223</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45223</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45223</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45223</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45223</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45223</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45223</v>
  